--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CIUDAD MOLINA BASKET.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CIUDAD MOLINA BASKET.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>29.7951</v>
+        <v>14.7447</v>
       </c>
       <c r="E2" t="n">
-        <v>29.4959</v>
+        <v>13.1975</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2988999999999997</v>
+        <v>1.546499999999999</v>
       </c>
       <c r="G2" t="n">
         <v>-5.4862</v>
@@ -610,13 +610,13 @@
         <v>42.7112</v>
       </c>
       <c r="S2" t="n">
-        <v>28.889</v>
+        <v>13.8387</v>
       </c>
       <c r="T2" t="n">
-        <v>24.414</v>
+        <v>8.115499999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>4.4751</v>
+        <v>5.7229</v>
       </c>
       <c r="V2" t="n">
         <v>0.2320000000000002</v>
@@ -643,13 +643,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>8.9315</v>
+        <v>8.0801</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.418699999999999</v>
+        <v>-2.8403</v>
       </c>
       <c r="F3" t="n">
-        <v>10.3501</v>
+        <v>10.92</v>
       </c>
       <c r="G3" t="n">
         <v>0.3067000000000002</v>
@@ -688,13 +688,13 @@
         <v>19.3022</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8286</v>
+        <v>1.977</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5634999999999999</v>
+        <v>-0.8582000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>2.265</v>
+        <v>2.8352</v>
       </c>
       <c r="V3" t="n">
         <v>-4.2655</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. KABASELE KASONGA</t>
+          <t>M. GARCIA ROSELLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>5.274900000000001</v>
+        <v>4.699799999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>6.76</v>
+        <v>0.9609999999999994</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.485199999999999</v>
+        <v>3.7389</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.8522</v>
+        <v>-4.592</v>
       </c>
       <c r="H4" t="n">
-        <v>1.791100000000001</v>
+        <v>0.3821999999999994</v>
       </c>
       <c r="I4" t="n">
-        <v>-7.6435</v>
+        <v>-4.974299999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7111</v>
+        <v>12.5277</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8299</v>
+        <v>8.7043</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8812000000000001</v>
+        <v>3.8233</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.5632</v>
+        <v>-17.1199</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0386</v>
+        <v>-8.3224</v>
       </c>
       <c r="O4" t="n">
-        <v>-8.524900000000001</v>
+        <v>-8.797499999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2053000000000002</v>
+        <v>9.4457</v>
       </c>
       <c r="Q4" t="n">
-        <v>-15.4006</v>
+        <v>-13.1418</v>
       </c>
       <c r="R4" t="n">
-        <v>15.1953</v>
+        <v>22.5876</v>
       </c>
       <c r="S4" t="n">
-        <v>15.6762</v>
+        <v>3.0471</v>
       </c>
       <c r="T4" t="n">
-        <v>12.8607</v>
+        <v>-0.5871000000000002</v>
       </c>
       <c r="U4" t="n">
-        <v>2.8158</v>
+        <v>3.6343</v>
       </c>
       <c r="V4" t="n">
-        <v>-4.3435</v>
+        <v>-3.2011</v>
       </c>
       <c r="W4" t="n">
-        <v>5.589</v>
+        <v>2.162</v>
       </c>
       <c r="X4" t="n">
-        <v>-9.9328</v>
+        <v>-5.363200000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GARCIA ROSELLO</t>
+          <t>A. LÓPEZ MARTINEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.976499999999999</v>
+        <v>0.6152</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.108</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>4.084300000000001</v>
+        <v>0.534</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.592</v>
+        <v>0.05160000000000009</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3821999999999994</v>
+        <v>-0.5616</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.974299999999999</v>
+        <v>0.613</v>
       </c>
       <c r="J5" t="n">
-        <v>12.5277</v>
+        <v>0.585</v>
       </c>
       <c r="K5" t="n">
-        <v>8.7043</v>
+        <v>0.0195</v>
       </c>
       <c r="L5" t="n">
-        <v>3.8233</v>
+        <v>0.5656</v>
       </c>
       <c r="M5" t="n">
-        <v>-17.1199</v>
+        <v>-0.5335000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.3224</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.797499999999999</v>
+        <v>0.04750000000000004</v>
       </c>
       <c r="P5" t="n">
-        <v>9.4457</v>
+        <v>1.4374</v>
       </c>
       <c r="Q5" t="n">
-        <v>-13.1418</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>22.5876</v>
+        <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3237</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.6559</v>
+        <v>-0.5038</v>
       </c>
       <c r="U5" t="n">
-        <v>3.9797</v>
+        <v>-0.1298</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.2011</v>
+        <v>-0.2402</v>
       </c>
       <c r="W5" t="n">
-        <v>2.162</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.363200000000001</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. LÓPEZ MARTINEZ</t>
+          <t>A. LUGO NITSCHE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1375</v>
+        <v>0.0302</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3372</v>
+        <v>0.0195</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4747</v>
+        <v>0.0107</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05160000000000009</v>
+        <v>-0.1752</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5616</v>
+        <v>-0.1752</v>
       </c>
       <c r="I6" t="n">
-        <v>0.613</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.585</v>
+        <v>0.0195</v>
       </c>
       <c r="K6" t="n">
         <v>0.0195</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5656</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5335000000000001</v>
+        <v>-0.1947</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.1947</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04750000000000004</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.4374</v>
+        <v>0.2053</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4374</v>
+        <v>0.2053</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1112</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9221999999999999</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1891</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LUGO NITSCHE</t>
+          <t>P. PARRA GOMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,61 +952,61 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0302</v>
+        <v>-0.1264000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0195</v>
+        <v>-2.1015</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0107</v>
+        <v>1.975</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1752</v>
+        <v>0.8693</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1752</v>
+        <v>1.0219</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.1524</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0195</v>
+        <v>0.3744</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0195</v>
+        <v>0.2954</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0789</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1947</v>
+        <v>0.495</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1947</v>
+        <v>0.7264999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.2313999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.03099999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.4224</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.4534</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>H. KABASELE KASONGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.06410000000000099</v>
+        <v>-1.586500000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>9.9588</v>
+        <v>-0.5737999999999998</v>
       </c>
       <c r="F8" t="n">
-        <v>-10.0226</v>
+        <v>-1.0128</v>
       </c>
       <c r="G8" t="n">
-        <v>-14.4646</v>
+        <v>-5.8522</v>
       </c>
       <c r="H8" t="n">
-        <v>-6.3884</v>
+        <v>1.791100000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-8.0764</v>
+        <v>-7.6435</v>
       </c>
       <c r="J8" t="n">
-        <v>6.8783</v>
+        <v>3.7111</v>
       </c>
       <c r="K8" t="n">
-        <v>4.9323</v>
+        <v>2.8299</v>
       </c>
       <c r="L8" t="n">
-        <v>1.9463</v>
+        <v>0.8812000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-21.3435</v>
+        <v>-9.5632</v>
       </c>
       <c r="N8" t="n">
-        <v>-11.3206</v>
+        <v>-1.0386</v>
       </c>
       <c r="O8" t="n">
-        <v>-10.023</v>
+        <v>-8.524900000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0268</v>
+        <v>-0.2053000000000002</v>
       </c>
       <c r="Q8" t="n">
-        <v>-22.9984</v>
+        <v>-15.4006</v>
       </c>
       <c r="R8" t="n">
-        <v>24.0249</v>
+        <v>15.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6223</v>
+        <v>8.8149</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4773</v>
+        <v>5.5268</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1451000000000001</v>
+        <v>3.2882</v>
       </c>
       <c r="V8" t="n">
-        <v>11.7518</v>
+        <v>-4.3435</v>
       </c>
       <c r="W8" t="n">
-        <v>24.6011</v>
+        <v>5.589</v>
       </c>
       <c r="X8" t="n">
-        <v>-12.8492</v>
+        <v>-9.9328</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. PARRA GOMEZ</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4889999999999999</v>
+        <v>-1.787199999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2061</v>
+        <v>7.2316</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7171</v>
+        <v>-9.018599999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8693</v>
+        <v>-14.4646</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0219</v>
+        <v>-6.3884</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1524</v>
+        <v>-8.0764</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3744</v>
+        <v>6.8783</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2954</v>
+        <v>4.9323</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0789</v>
+        <v>1.9463</v>
       </c>
       <c r="M9" t="n">
-        <v>0.495</v>
+        <v>-21.3435</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7264999999999999</v>
+        <v>-11.3206</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2313999999999999</v>
+        <v>-10.023</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.0267</v>
+        <v>1.0268</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0534</v>
+        <v>-22.9984</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0267</v>
+        <v>24.0249</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3316</v>
+        <v>-0.1011999999999997</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.527</v>
+        <v>-1.25</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1954</v>
+        <v>1.1489</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>11.7518</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>24.6011</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-12.8492</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8291</v>
+        <v>-2.4171</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2776</v>
+        <v>1.1344</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1067</v>
+        <v>-3.5514</v>
       </c>
       <c r="G10" t="n">
         <v>0.588</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4009</v>
+        <v>-0.9889000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6859000000000001</v>
+        <v>-0.8294</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2851</v>
+        <v>-0.1597</v>
       </c>
       <c r="V10" t="n">
         <v>-2.8377</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. CADME ARIAS</t>
+          <t>J. TAVELLI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.040800000000001</v>
+        <v>-2.824599999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7153</v>
+        <v>-1.7606</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.3255</v>
+        <v>-1.064</v>
       </c>
       <c r="G11" t="n">
-        <v>-8.819800000000001</v>
+        <v>11.9143</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.9653</v>
+        <v>12.2067</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8546</v>
+        <v>-0.2922000000000007</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3651</v>
+        <v>31.1463</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3825</v>
+        <v>22.4041</v>
       </c>
       <c r="L11" t="n">
-        <v>2.7474</v>
+        <v>8.742100000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-10.1849</v>
+        <v>-19.2321</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.5828</v>
+        <v>-10.1975</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.601900000000001</v>
+        <v>-9.0344</v>
       </c>
       <c r="P11" t="n">
-        <v>1.026600000000001</v>
+        <v>-8.0083</v>
       </c>
       <c r="Q11" t="n">
-        <v>-11.7044</v>
+        <v>-46.20189999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>12.7312</v>
+        <v>38.194</v>
       </c>
       <c r="S11" t="n">
-        <v>5.8722</v>
+        <v>0.3200999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>5.5462</v>
+        <v>-3.8628</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3258</v>
+        <v>4.1828</v>
       </c>
       <c r="V11" t="n">
-        <v>-6.1197</v>
+        <v>-7.051</v>
       </c>
       <c r="W11" t="n">
-        <v>3.0779</v>
+        <v>17.1575</v>
       </c>
       <c r="X11" t="n">
-        <v>-9.197800000000001</v>
+        <v>-24.2084</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.3972</v>
+        <v>-8.969299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.7977</v>
+        <v>-6.8561</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5997</v>
+        <v>-2.1134</v>
       </c>
       <c r="G12" t="n">
         <v>-5.144</v>
@@ -1390,13 +1390,13 @@
         <v>5.7495</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.6398</v>
+        <v>-1.2118</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.3753</v>
+        <v>-1.4339</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2642</v>
+        <v>0.2221</v>
       </c>
       <c r="V12" t="n">
         <v>-4.0508</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. TAVELLI</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.1055</v>
+        <v>-10.5561</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.6171</v>
+        <v>-4.244100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4884</v>
+        <v>-6.312200000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>11.9143</v>
+        <v>-18.6351</v>
       </c>
       <c r="H13" t="n">
-        <v>12.2067</v>
+        <v>-10.0046</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2922000000000007</v>
+        <v>-8.6304</v>
       </c>
       <c r="J13" t="n">
-        <v>31.1463</v>
+        <v>2.319</v>
       </c>
       <c r="K13" t="n">
-        <v>22.4041</v>
+        <v>1.4814</v>
       </c>
       <c r="L13" t="n">
-        <v>8.742100000000001</v>
+        <v>0.8379000000000002</v>
       </c>
       <c r="M13" t="n">
-        <v>-19.2321</v>
+        <v>-20.9542</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.1975</v>
+        <v>-11.486</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.0344</v>
+        <v>-9.468299999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-8.0083</v>
+        <v>8.4192</v>
       </c>
       <c r="Q13" t="n">
-        <v>-46.20189999999999</v>
+        <v>-14.9898</v>
       </c>
       <c r="R13" t="n">
-        <v>38.194</v>
+        <v>23.4089</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.960699999999999</v>
+        <v>-4.7917</v>
       </c>
       <c r="T13" t="n">
-        <v>-12.7193</v>
+        <v>-0.8934</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7588</v>
+        <v>-3.8984</v>
       </c>
       <c r="V13" t="n">
-        <v>-7.051</v>
+        <v>4.451700000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>17.1575</v>
+        <v>9.32</v>
       </c>
       <c r="X13" t="n">
-        <v>-24.2084</v>
+        <v>-4.8683</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>G. CADME ARIAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.3687</v>
+        <v>-10.868</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.273199999999999</v>
+        <v>-5.0586</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.0954</v>
+        <v>-5.8093</v>
       </c>
       <c r="G14" t="n">
-        <v>-18.6351</v>
+        <v>-8.819800000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.0046</v>
+        <v>-6.9653</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.6304</v>
+        <v>-1.8546</v>
       </c>
       <c r="J14" t="n">
-        <v>2.319</v>
+        <v>1.3651</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4814</v>
+        <v>-1.3825</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8379000000000002</v>
+        <v>2.7474</v>
       </c>
       <c r="M14" t="n">
-        <v>-20.9542</v>
+        <v>-10.1849</v>
       </c>
       <c r="N14" t="n">
-        <v>-11.486</v>
+        <v>-5.5828</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.468299999999999</v>
+        <v>-4.601900000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>8.4192</v>
+        <v>1.026600000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.9898</v>
+        <v>-11.7044</v>
       </c>
       <c r="R14" t="n">
-        <v>23.4089</v>
+        <v>12.7312</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.6044</v>
+        <v>3.0451</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.922499999999999</v>
+        <v>2.203</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.682099999999999</v>
+        <v>0.8418000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>4.451700000000001</v>
+        <v>-6.1197</v>
       </c>
       <c r="W14" t="n">
-        <v>9.32</v>
+        <v>3.0779</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.8683</v>
+        <v>-9.197800000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-33.9624</v>
+        <v>-19.401</v>
       </c>
       <c r="E15" t="n">
-        <v>-16.2092</v>
+        <v>-7.9764</v>
       </c>
       <c r="F15" t="n">
-        <v>-17.7539</v>
+        <v>-11.4247</v>
       </c>
       <c r="G15" t="n">
         <v>-13.9188</v>
@@ -1624,13 +1624,13 @@
         <v>41.6848</v>
       </c>
       <c r="S15" t="n">
-        <v>-17.4235</v>
+        <v>-2.8616</v>
       </c>
       <c r="T15" t="n">
-        <v>-11.271</v>
+        <v>-3.0381</v>
       </c>
       <c r="U15" t="n">
-        <v>-6.152500000000001</v>
+        <v>0.1762000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>6.2091</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-37.4465</v>
+        <v>-23.5455</v>
       </c>
       <c r="E16" t="n">
-        <v>-32.4005</v>
+        <v>-22.7963</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.046100000000001</v>
+        <v>-0.7494000000000005</v>
       </c>
       <c r="G16" t="n">
         <v>-33.3405</v>
@@ -1702,13 +1702,13 @@
         <v>40.6577</v>
       </c>
       <c r="S16" t="n">
-        <v>-13.5728</v>
+        <v>0.3278999999999997</v>
       </c>
       <c r="T16" t="n">
-        <v>-12.1968</v>
+        <v>-2.5924</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3762</v>
+        <v>2.920500000000001</v>
       </c>
       <c r="V16" t="n">
         <v>12.7521</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>A. DUVAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-47.782</v>
+        <v>-37.4344</v>
       </c>
       <c r="E17" t="n">
-        <v>-25.9731</v>
+        <v>-29.4236</v>
       </c>
       <c r="F17" t="n">
-        <v>-21.809</v>
+        <v>-8.0106</v>
       </c>
       <c r="G17" t="n">
-        <v>-32.7185</v>
+        <v>-47.2194</v>
       </c>
       <c r="H17" t="n">
-        <v>-18.3389</v>
+        <v>-18.6631</v>
       </c>
       <c r="I17" t="n">
-        <v>-14.3797</v>
+        <v>-28.5562</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5381999999999996</v>
+        <v>-14.2522</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.289100000000001</v>
+        <v>-5.6469</v>
       </c>
       <c r="L17" t="n">
-        <v>3.827</v>
+        <v>-8.604900000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-33.2566</v>
+        <v>-32.9673</v>
       </c>
       <c r="N17" t="n">
-        <v>-15.0503</v>
+        <v>-13.0163</v>
       </c>
       <c r="O17" t="n">
-        <v>-18.2066</v>
+        <v>-19.9517</v>
       </c>
       <c r="P17" t="n">
-        <v>-16.0168</v>
+        <v>6.9818</v>
       </c>
       <c r="Q17" t="n">
-        <v>-48.4605</v>
+        <v>-27.5159</v>
       </c>
       <c r="R17" t="n">
-        <v>32.4443</v>
+        <v>34.4977</v>
       </c>
       <c r="S17" t="n">
-        <v>12.4864</v>
+        <v>-0.4088</v>
       </c>
       <c r="T17" t="n">
-        <v>5.249899999999999</v>
+        <v>-3.7889</v>
       </c>
       <c r="U17" t="n">
-        <v>7.2367</v>
+        <v>3.3802</v>
       </c>
       <c r="V17" t="n">
-        <v>-11.5335</v>
+        <v>3.212399999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>16.6999</v>
+        <v>16.1326</v>
       </c>
       <c r="X17" t="n">
-        <v>-28.2331</v>
+        <v>-12.9206</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DUVAL</t>
+          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-51.8751</v>
+        <v>-52.3509</v>
       </c>
       <c r="E18" t="n">
-        <v>-38.6598</v>
+        <v>-23.7529</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.2152</v>
+        <v>-28.598</v>
       </c>
       <c r="G18" t="n">
-        <v>-47.2194</v>
+        <v>-29.8525</v>
       </c>
       <c r="H18" t="n">
-        <v>-18.6631</v>
+        <v>-13.8371</v>
       </c>
       <c r="I18" t="n">
-        <v>-28.5562</v>
+        <v>-16.0153</v>
       </c>
       <c r="J18" t="n">
-        <v>-14.2522</v>
+        <v>-4.0032</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.6469</v>
+        <v>-3.5366</v>
       </c>
       <c r="L18" t="n">
-        <v>-8.604900000000001</v>
+        <v>-0.4673999999999997</v>
       </c>
       <c r="M18" t="n">
-        <v>-32.9673</v>
+        <v>-25.8489</v>
       </c>
       <c r="N18" t="n">
-        <v>-13.0163</v>
+        <v>-10.3009</v>
       </c>
       <c r="O18" t="n">
-        <v>-19.9517</v>
+        <v>-15.5482</v>
       </c>
       <c r="P18" t="n">
-        <v>6.9818</v>
+        <v>3.6963</v>
       </c>
       <c r="Q18" t="n">
-        <v>-27.5159</v>
+        <v>-20.3286</v>
       </c>
       <c r="R18" t="n">
-        <v>34.4977</v>
+        <v>24.0248</v>
       </c>
       <c r="S18" t="n">
-        <v>-14.8494</v>
+        <v>-1.5182</v>
       </c>
       <c r="T18" t="n">
-        <v>-13.025</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.8243</v>
+        <v>-0.9195</v>
       </c>
       <c r="V18" t="n">
-        <v>3.212399999999999</v>
+        <v>-24.6763</v>
       </c>
       <c r="W18" t="n">
-        <v>16.1326</v>
+        <v>1.1786</v>
       </c>
       <c r="X18" t="n">
-        <v>-12.9206</v>
+        <v>-25.8549</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-55.5574</v>
+        <v>-56.8712</v>
       </c>
       <c r="E19" t="n">
-        <v>-24.8685</v>
+        <v>-31.0793</v>
       </c>
       <c r="F19" t="n">
-        <v>-30.6889</v>
+        <v>-25.7918</v>
       </c>
       <c r="G19" t="n">
-        <v>-29.8525</v>
+        <v>-32.7185</v>
       </c>
       <c r="H19" t="n">
-        <v>-13.8371</v>
+        <v>-18.3389</v>
       </c>
       <c r="I19" t="n">
-        <v>-16.0153</v>
+        <v>-14.3797</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.0032</v>
+        <v>0.5381999999999996</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.5366</v>
+        <v>-3.289100000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4673999999999997</v>
+        <v>3.827</v>
       </c>
       <c r="M19" t="n">
-        <v>-25.8489</v>
+        <v>-33.2566</v>
       </c>
       <c r="N19" t="n">
-        <v>-10.3009</v>
+        <v>-15.0503</v>
       </c>
       <c r="O19" t="n">
-        <v>-15.5482</v>
+        <v>-18.2066</v>
       </c>
       <c r="P19" t="n">
-        <v>3.6963</v>
+        <v>-16.0168</v>
       </c>
       <c r="Q19" t="n">
-        <v>-20.3286</v>
+        <v>-48.4605</v>
       </c>
       <c r="R19" t="n">
-        <v>24.0248</v>
+        <v>32.4443</v>
       </c>
       <c r="S19" t="n">
-        <v>-4.7249</v>
+        <v>3.3976</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.715</v>
+        <v>0.1435</v>
       </c>
       <c r="U19" t="n">
-        <v>-3.0097</v>
+        <v>3.2539</v>
       </c>
       <c r="V19" t="n">
-        <v>-24.6763</v>
+        <v>-11.5335</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1786</v>
+        <v>16.6999</v>
       </c>
       <c r="X19" t="n">
-        <v>-25.8549</v>
+        <v>-28.2331</v>
       </c>
     </row>
     <row r="20">
@@ -1969,25 +1969,25 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-229.7721</v>
+        <v>-200.5682</v>
       </c>
       <c r="E20" t="n">
-        <v>-124.0726</v>
+        <v>-115.8383</v>
       </c>
       <c r="F20" t="n">
-        <v>-105.7008</v>
+        <v>-84.7311</v>
       </c>
       <c r="G20" t="n">
         <v>-206.4889</v>
       </c>
       <c r="H20" t="n">
-        <v>-69.60470000000001</v>
+        <v>-69.60469999999999</v>
       </c>
       <c r="I20" t="n">
         <v>-136.8844</v>
       </c>
       <c r="J20" t="n">
-        <v>94.4151</v>
+        <v>94.41510000000001</v>
       </c>
       <c r="K20" t="n">
         <v>70.8824</v>
@@ -2005,7 +2005,7 @@
         <v>-160.418</v>
       </c>
       <c r="P20" t="n">
-        <v>13.3477</v>
+        <v>13.34770000000001</v>
       </c>
       <c r="Q20" t="n">
         <v>-367.5613</v>
@@ -2014,13 +2014,13 @@
         <v>380.9102</v>
       </c>
       <c r="S20" t="n">
-        <v>-6.920799999999991</v>
+        <v>22.2836</v>
       </c>
       <c r="T20" t="n">
-        <v>-12.9043</v>
+        <v>-4.670900000000003</v>
       </c>
       <c r="U20" t="n">
-        <v>5.984400000000003</v>
+        <v>26.953</v>
       </c>
       <c r="V20" t="n">
         <v>-29.7102</v>
